--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_los_lagos.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:48</t>
+    <t xml:space="preserve">2026-09-24 00:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -932,7 +932,7 @@
         <v>-0.77</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.02</v>
@@ -955,7 +955,7 @@
         <v>-0.22</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.22</v>
@@ -978,7 +978,7 @@
         <v>-0.66</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.12</v>
@@ -1001,7 +1001,7 @@
         <v>-0.41</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.23</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_los_lagos.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:38</t>
+    <t xml:space="preserve">2026-10-01 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_los_lagos.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:12</t>
+    <t xml:space="preserve">2026-10-05 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
